--- a/Team-Data/2013-14/12-26-2013-14.xlsx
+++ b/Team-Data/2013-14/12-26-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,49 +728,49 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>0.552</v>
+        <v>0.536</v>
       </c>
       <c r="H2" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="J2" t="n">
-        <v>83.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="O2" t="n">
         <v>15.9</v>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
         <v>32.2</v>
@@ -712,52 +779,52 @@
         <v>41.3</v>
       </c>
       <c r="U2" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="V2" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="X2" t="n">
         <v>4.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AA2" t="n">
         <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.2</v>
+        <v>102.3</v>
       </c>
       <c r="AC2" t="n">
         <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI2" t="n">
         <v>9</v>
       </c>
-      <c r="AG2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
         <v>4</v>
@@ -766,19 +833,19 @@
         <v>6</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -793,10 +860,10 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>24</v>
@@ -805,13 +872,13 @@
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
@@ -936,7 +1003,7 @@
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -960,7 +1027,7 @@
         <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>23</v>
@@ -981,7 +1048,7 @@
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1115,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>12</v>
@@ -1297,13 +1364,13 @@
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
         <v>29</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -1467,19 +1534,19 @@
         <v>-0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
         <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1488,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -1571,121 +1638,121 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="H7" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="I7" t="n">
-        <v>36.8</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>85.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.428</v>
+        <v>0.424</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
         <v>20.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P7" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R7" t="n">
         <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T7" t="n">
         <v>43.6</v>
       </c>
       <c r="U7" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V7" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z7" t="n">
         <v>19.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.5</v>
+        <v>95.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN7" t="n">
         <v>18</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>17</v>
-      </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ7" t="n">
         <v>19</v>
@@ -1694,7 +1761,7 @@
         <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
@@ -1703,22 +1770,22 @@
         <v>27</v>
       </c>
       <c r="AV7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AW7" t="n">
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AY7" t="n">
         <v>22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
         <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.552</v>
+        <v>0.571</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1777,61 +1844,61 @@
         <v>0.466</v>
       </c>
       <c r="L8" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="P8" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.805</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R8" t="n">
         <v>10.1</v>
       </c>
       <c r="S8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
         <v>40.7</v>
       </c>
       <c r="U8" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
         <v>14.6</v>
       </c>
       <c r="W8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X8" t="n">
         <v>4.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.9</v>
+        <v>103.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1840,10 +1907,10 @@
         <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1861,13 +1928,13 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,13 +1943,13 @@
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
         <v>27</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>8</v>
@@ -1891,19 +1958,19 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
         <v>12</v>
@@ -2043,7 +2110,7 @@
         <v>16</v>
       </c>
       <c r="AN9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -2195,25 +2262,25 @@
         <v>-0.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>12</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
         <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>12</v>
@@ -2228,7 +2295,7 @@
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>9</v>
@@ -2249,7 +2316,7 @@
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
@@ -2261,7 +2328,7 @@
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
@@ -2404,10 +2471,10 @@
         <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
         <v>20</v>
@@ -2431,10 +2498,10 @@
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -2449,7 +2516,7 @@
         <v>19</v>
       </c>
       <c r="BB11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -2481,97 +2548,97 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.645</v>
+        <v>0.633</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
-        <v>78.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="M12" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.353</v>
+        <v>0.358</v>
       </c>
       <c r="O12" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="P12" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.698</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
         <v>34.6</v>
       </c>
       <c r="T12" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U12" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V12" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="X12" t="n">
         <v>6.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.3</v>
+        <v>106.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG12" t="n">
         <v>7</v>
       </c>
-      <c r="AG12" t="n">
-        <v>6</v>
-      </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>14</v>
@@ -2583,16 +2650,16 @@
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2601,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2613,25 +2680,25 @@
         <v>17</v>
       </c>
       <c r="AV12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -2741,22 +2808,22 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ13" t="n">
         <v>27</v>
@@ -2807,7 +2874,7 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -2845,103 +2912,103 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.645</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="J14" t="n">
-        <v>82.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L14" t="n">
         <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N14" t="n">
-        <v>0.335</v>
+        <v>0.333</v>
       </c>
       <c r="O14" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="P14" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.717</v>
+        <v>0.72</v>
       </c>
       <c r="R14" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S14" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>4.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z14" t="n">
         <v>22.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.2</v>
+        <v>105</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>7</v>
@@ -2953,7 +3020,7 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2971,19 +3038,19 @@
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -2992,7 +3059,7 @@
         <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-4</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG15" t="n">
         <v>18</v>
@@ -3123,16 +3190,16 @@
         <v>17</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK15" t="n">
         <v>22</v>
       </c>
       <c r="AL15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM15" t="n">
         <v>4</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>5</v>
       </c>
       <c r="AN15" t="n">
         <v>10</v>
@@ -3150,16 +3217,16 @@
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>24</v>
@@ -3171,10 +3238,10 @@
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,43 +3294,43 @@
         <v>36.7</v>
       </c>
       <c r="J16" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L16" t="n">
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O16" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="P16" t="n">
         <v>20.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.758</v>
+        <v>0.765</v>
       </c>
       <c r="R16" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="S16" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
         <v>21.3</v>
       </c>
       <c r="V16" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W16" t="n">
         <v>7.2</v>
@@ -3275,34 +3342,34 @@
         <v>5.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="AA16" t="n">
         <v>19.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="AC16" t="n">
-        <v>-3.4</v>
+        <v>-3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
       </c>
       <c r="AF16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
         <v>19</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
@@ -3317,28 +3384,28 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS16" t="n">
         <v>21</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>21</v>
       </c>
       <c r="AU16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3350,10 +3417,10 @@
         <v>28</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
@@ -3499,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
@@ -3508,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3681,19 +3748,19 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ18" t="n">
         <v>6</v>
       </c>
       <c r="AR18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>2.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3845,28 +3912,28 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>13</v>
       </c>
       <c r="AM19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3881,10 +3948,10 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -4027,10 +4094,10 @@
         <v>17</v>
       </c>
       <c r="AH20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI20" t="n">
         <v>6</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>7</v>
       </c>
       <c r="AJ20" t="n">
         <v>4</v>
@@ -4045,7 +4112,7 @@
         <v>27</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>13</v>
@@ -4087,7 +4154,7 @@
         <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>24</v>
@@ -4209,7 +4276,7 @@
         <v>24</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>25</v>
@@ -4224,16 +4291,16 @@
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
         <v>11</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX21" t="n">
         <v>16</v>
@@ -4266,7 +4333,7 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4446,22 @@
         <v>7.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>15</v>
@@ -4409,10 +4476,10 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP22" t="n">
         <v>5</v>
@@ -4451,7 +4518,7 @@
         <v>13</v>
       </c>
       <c r="BB22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,13 +4640,13 @@
         <v>27</v>
       </c>
       <c r="AH23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
         <v>19</v>
@@ -4606,7 +4673,7 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
         <v>19</v>
@@ -4618,10 +4685,10 @@
         <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY23" t="n">
         <v>24</v>
@@ -4630,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>26</v>
@@ -4794,13 +4861,13 @@
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
         <v>26</v>
@@ -4815,7 +4882,7 @@
         <v>20</v>
       </c>
       <c r="BB24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
         <v>8</v>
@@ -4940,10 +5007,10 @@
         <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>15</v>
@@ -4967,13 +5034,13 @@
         <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
         <v>28</v>
@@ -4982,7 +5049,7 @@
         <v>23</v>
       </c>
       <c r="AW25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
@@ -4997,7 +5064,7 @@
         <v>15</v>
       </c>
       <c r="BB25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -5029,85 +5096,85 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.828</v>
+        <v>0.821</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="J26" t="n">
-        <v>87.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M26" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>0.403</v>
+        <v>0.405</v>
       </c>
       <c r="O26" t="n">
         <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.819</v>
       </c>
       <c r="R26" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="S26" t="n">
-        <v>33.1</v>
+        <v>32.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.4</v>
+        <v>45.9</v>
       </c>
       <c r="U26" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V26" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W26" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
         <v>20.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>108.7</v>
+        <v>108.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5134,10 +5201,10 @@
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
         <v>11</v>
@@ -5152,22 +5219,22 @@
         <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AT26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5301,13 +5368,13 @@
         <v>26</v>
       </c>
       <c r="AH27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>16</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>17</v>
       </c>
       <c r="AK27" t="n">
         <v>20</v>
@@ -5346,7 +5413,7 @@
         <v>9</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.767</v>
+        <v>0.759</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.485</v>
+        <v>0.484</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.398</v>
+        <v>0.397</v>
       </c>
       <c r="O28" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="P28" t="n">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.762</v>
+        <v>0.756</v>
       </c>
       <c r="R28" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U28" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
         <v>8</v>
@@ -5456,25 +5523,25 @@
         <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.6</v>
+        <v>103.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AD28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE28" t="n">
         <v>4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>5</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5507,10 +5574,10 @@
         <v>30</v>
       </c>
       <c r="AP28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
@@ -5519,7 +5586,7 @@
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -5665,10 +5732,10 @@
         <v>20</v>
       </c>
       <c r="AH29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
         <v>14</v>
@@ -5701,7 +5768,7 @@
         <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU29" t="n">
         <v>29</v>
@@ -5713,7 +5780,7 @@
         <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5920,7 @@
         <v>26</v>
       </c>
       <c r="AJ30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="n">
         <v>24</v>
@@ -5889,7 +5956,7 @@
         <v>25</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>17</v>
       </c>
       <c r="AF31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
@@ -6035,7 +6102,7 @@
         <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>17</v>
@@ -6050,7 +6117,7 @@
         <v>4</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
@@ -6062,7 +6129,7 @@
         <v>15</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-26-2013-14</t>
+          <t>2013-12-26</t>
         </is>
       </c>
     </row>
